--- a/SGC-CKN/Excel/4576000e-8e19-4844-8229-3f0378c0022c_Hạng_mục__Thi_công_cọc_khoan_nhồi__tường_vây_cho_các_hạng_mục_Lô_CT-02_P1_02_D800_31-03-2026.xlsx
+++ b/SGC-CKN/Excel/4576000e-8e19-4844-8229-3f0378c0022c_Hạng_mục__Thi_công_cọc_khoan_nhồi__tường_vây_cho_các_hạng_mục_Lô_CT-02_P1_02_D800_31-03-2026.xlsx
@@ -102,7 +102,7 @@
 31/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">09:05
+    <t xml:space="preserve">09:15
 31/03/2026</t>
   </si>
   <si>
@@ -115,7 +115,7 @@
     <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
   </si>
   <si>
-    <t xml:space="preserve">10:18
+    <t xml:space="preserve">10:58
 31/03/2026</t>
   </si>
   <si>
@@ -1165,13 +1165,13 @@
         <v>-2.11</v>
       </c>
       <c r="H11" s="5">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="I11" s="5">
         <v>1.09</v>
       </c>
       <c r="J11" s="8">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1200,13 +1200,13 @@
         <v>-5.21</v>
       </c>
       <c r="H12" s="9">
-        <v>1.32</v>
+        <v>0.65</v>
       </c>
       <c r="I12" s="9">
         <v>3.1</v>
       </c>
       <c r="J12" s="8">
-        <v>2.35</v>
+        <v>4.77</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>35</v>
@@ -1232,16 +1232,16 @@
         <v>-5.21</v>
       </c>
       <c r="G13" s="12">
-        <v>-8.7</v>
+        <v>-8.3</v>
       </c>
       <c r="H13" s="12">
         <v>2.38</v>
       </c>
       <c r="I13" s="12">
-        <v>3.49</v>
+        <v>3.09</v>
       </c>
       <c r="J13" s="8">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="K13" s="13" t="s">
         <v>35</v>
@@ -1264,7 +1264,7 @@
         <v>41</v>
       </c>
       <c r="F14" s="15">
-        <v>-8.7</v>
+        <v>-8.3</v>
       </c>
       <c r="G14" s="15">
         <v>-17.3</v>
@@ -1273,10 +1273,10 @@
         <v>0.67</v>
       </c>
       <c r="I14" s="15">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="J14" s="18">
-        <v>12.9</v>
+        <v>13.5</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>35</v>
@@ -1407,16 +1407,16 @@
         <v>-39.5</v>
       </c>
       <c r="G18" s="28">
-        <v>-44.71</v>
+        <v>-44.41</v>
       </c>
       <c r="H18" s="28">
         <v>1.55</v>
       </c>
       <c r="I18" s="28">
-        <v>5.21</v>
+        <v>4.91</v>
       </c>
       <c r="J18" s="8">
-        <v>3.36</v>
+        <v>3.17</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>35</v>
@@ -1577,13 +1577,13 @@
         <v>-2.11</v>
       </c>
       <c r="G2" s="5">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="H2" s="5">
         <v>1.09</v>
       </c>
       <c r="I2" s="8">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1606,13 +1606,13 @@
         <v>-5.21</v>
       </c>
       <c r="G3" s="9">
-        <v>1.32</v>
+        <v>0.65</v>
       </c>
       <c r="H3" s="9">
         <v>3.1</v>
       </c>
       <c r="I3" s="8">
-        <v>2.35</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1632,16 +1632,16 @@
         <v>-5.21</v>
       </c>
       <c r="F4" s="12">
-        <v>-8.7</v>
+        <v>-8.3</v>
       </c>
       <c r="G4" s="12">
         <v>2.38</v>
       </c>
       <c r="H4" s="12">
-        <v>3.49</v>
+        <v>3.09</v>
       </c>
       <c r="I4" s="8">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1658,7 +1658,7 @@
         <v>1</v>
       </c>
       <c r="E5" s="15">
-        <v>-8.7</v>
+        <v>-8.3</v>
       </c>
       <c r="F5" s="15">
         <v>-17.3</v>
@@ -1667,10 +1667,10 @@
         <v>0.67</v>
       </c>
       <c r="H5" s="15">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="I5" s="18">
-        <v>12.9</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1777,16 +1777,16 @@
         <v>-39.5</v>
       </c>
       <c r="F9" s="28">
-        <v>-44.71</v>
+        <v>-44.41</v>
       </c>
       <c r="G9" s="28">
         <v>1.55</v>
       </c>
       <c r="H9" s="28">
-        <v>5.21</v>
+        <v>4.91</v>
       </c>
       <c r="I9" s="8">
-        <v>3.36</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1806,16 +1806,16 @@
         <v>-1.02</v>
       </c>
       <c r="F10" s="33">
-        <v>-44.71</v>
+        <v>-44.41</v>
       </c>
       <c r="G10" s="33">
-        <v>8.33</v>
+        <v>7.83</v>
       </c>
       <c r="H10" s="33">
-        <v>43.69</v>
+        <v>43.39</v>
       </c>
       <c r="I10" s="33">
-        <v>5.24</v>
+        <v>5.54</v>
       </c>
     </row>
   </sheetData>
